--- a/docs/testing/PPT问答系统测试用例集.xlsx
+++ b/docs/testing/PPT问答系统测试用例集.xlsx
@@ -11,7 +11,7 @@
     <sheet name="统计" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试用例'!$A$1:$K$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试用例'!$A$1:$K$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3095,8 +3095,64 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>DEL-008</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>文档删除</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>硬删除后 parsed 磁盘目录零残留（含图片产物）</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>回归测试</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>上传含图片文档并解析成功</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>1.硬删除该文档
+2.检查响应 warnings 与 /app/storage/parsed/{doc}/ 目录</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>PG/Qdrant/磁盘三处零残留，warnings 为空</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>场景法</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K46"/>
+  <autoFilter ref="A1:K47"/>
   <conditionalFormatting sqref="K2:K46">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"通过"</formula>
@@ -3267,7 +3323,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -3317,7 +3373,7 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -3327,10 +3383,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -3340,10 +3396,10 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/docs/testing/PPT问答系统测试用例集.xlsx
+++ b/docs/testing/PPT问答系统测试用例集.xlsx
@@ -3147,7 +3147,7 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>失败</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">

--- a/docs/testing/PPT问答系统测试用例集.xlsx
+++ b/docs/testing/PPT问答系统测试用例集.xlsx
@@ -630,7 +630,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>未执行</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>未执行</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>未执行</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>未执行</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>未执行</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>未执行</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>未执行</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>未执行</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>未执行</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>未执行</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>未执行</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>未执行</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>未执行</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>未执行</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>未执行</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -3294,7 +3294,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
